--- a/etf_holdings/2026-09-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2475</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.93%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5285</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.16%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1185</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.6%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>5050</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.45%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3555</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+7.96%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>6920</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.22%580</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.22%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>580</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.53%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1910</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.65%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5415</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.75%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>154</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.26%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1895</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.48%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1240</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.48%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>2115</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.87%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>699</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:32</t>
+          <t>2026-09-26 21:23:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2340</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:36</t>
+          <t>2026-09-26 21:23:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:37</t>
+          <t>2026-09-26 21:23:27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:38</t>
+          <t>2026-09-26 21:23:38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:38</t>
+          <t>2026-09-26 21:23:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:38</t>
+          <t>2026-09-26 21:23:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:38</t>
+          <t>2026-09-26 21:23:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:38</t>
+          <t>2026-09-26 21:23:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-26 21:14:38</t>
+          <t>2026-09-26 21:23:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-26_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-26_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2475</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.93%5285</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.93%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5285</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.16%1185</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.16%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1185</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.6%5050</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>5050</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.45%3555</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.45%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3555</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+7.96%6920</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+7.96%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6920</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.22%580</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>580</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.53%1910</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.53%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1910</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.65%5415</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.65%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5415</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.75%154</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.75%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>154</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.26%1895</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.26%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1895</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.48%1240</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.48%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1240</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.48%2115</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2115</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.87%699</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.87%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>699</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:04</t>
+          <t>2026-09-26 21:45:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%2340</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2340</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:16</t>
+          <t>2026-09-26 21:45:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:27</t>
+          <t>2026-09-26 21:45:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:38</t>
+          <t>2026-09-26 21:45:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:38</t>
+          <t>2026-09-26 21:45:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:38</t>
+          <t>2026-09-26 21:45:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:38</t>
+          <t>2026-09-26 21:45:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:38</t>
+          <t>2026-09-26 21:45:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-26 21:23:38</t>
+          <t>2026-09-26 21:45:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
